--- a/artfynd/Börsåsen N artfynd.xlsx
+++ b/artfynd/Börsåsen N artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY61"/>
+  <dimension ref="A1:AY64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6877,6 +6877,297 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>135234495</v>
+      </c>
+      <c r="B62" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Bursnäs, Hjd</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>492573</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6917555</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Överhogdal</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Teo Jernkvist</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Teo Jernkvist</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>135234497</v>
+      </c>
+      <c r="B63" t="n">
+        <v>78776</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Bursnäs, Hjd</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>492725</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6917603</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Överhogdal</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Teo Jernkvist</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Teo Jernkvist</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>135234496</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Bursnäs, Hjd</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>492726</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6917600</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Överhogdal</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Teo Jernkvist</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Teo Jernkvist</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
